--- a/predict_droughts.xlsx
+++ b/predict_droughts.xlsx
@@ -480,19 +480,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>30.542368</v>
+        <v>32.76202</v>
       </c>
       <c r="E2" t="n">
         <v>0.999999507</v>
       </c>
       <c r="F2" t="n">
-        <v>2.774125</v>
+        <v>2.794999</v>
       </c>
       <c r="G2" t="n">
         <v>0.981553205</v>
       </c>
       <c r="H2" t="n">
-        <v>0.786539</v>
+        <v>0.779465</v>
       </c>
       <c r="I2" t="n">
         <v>15578246.18679993</v>
@@ -515,19 +515,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>32.289423</v>
+        <v>32.54072</v>
       </c>
       <c r="E3" t="n">
         <v>0.9999999939999999</v>
       </c>
       <c r="F3" t="n">
-        <v>2.803005</v>
+        <v>2.756854</v>
       </c>
       <c r="G3" t="n">
         <v>0.999992707</v>
       </c>
       <c r="H3" t="n">
-        <v>0.678955</v>
+        <v>0.662013</v>
       </c>
       <c r="I3" t="n">
         <v>15915830.99439867</v>
@@ -550,19 +550,19 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>33.378304</v>
+        <v>33.689877</v>
       </c>
       <c r="E4" t="n">
         <v>0.999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>2.897074</v>
+        <v>2.830399</v>
       </c>
       <c r="G4" t="n">
         <v>0.999988585</v>
       </c>
       <c r="H4" t="n">
-        <v>0.682929</v>
+        <v>0.677614</v>
       </c>
       <c r="I4" t="n">
         <v>15915738.2471999</v>
@@ -585,19 +585,19 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>31.175358</v>
+        <v>32.314749</v>
       </c>
       <c r="E5" t="n">
         <v>0.999999853</v>
       </c>
       <c r="F5" t="n">
-        <v>2.703907</v>
+        <v>2.776965</v>
       </c>
       <c r="G5" t="n">
         <v>0.978041676</v>
       </c>
       <c r="H5" t="n">
-        <v>0.717535</v>
+        <v>0.720898</v>
       </c>
       <c r="I5" t="n">
         <v>15514386.44679999</v>
